--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DB\Projects\SW002-LoadWizardPro_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449CDF3B-7BAC-4060-A6EB-6B8B11CED337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBF0D35-DEFC-4BF8-8BD5-93CCA22F1E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Robot FieldBus" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="281">
   <si>
     <t>Сигналы от Робота к ПЛК</t>
   </si>
@@ -162,18 +162,6 @@
     <t>Патрон 1 закрыт</t>
   </si>
   <si>
-    <t>Открыть патрон 2</t>
-  </si>
-  <si>
-    <t>Патрон 2 открыт</t>
-  </si>
-  <si>
-    <t>Закрыть патрон 2</t>
-  </si>
-  <si>
-    <t>Патрон 2 закрыт</t>
-  </si>
-  <si>
     <t>Загрузка завершена</t>
   </si>
   <si>
@@ -273,108 +261,30 @@
     <t>Работа с полкой 4 завершена</t>
   </si>
   <si>
-    <t>Состояние захвата 1</t>
-  </si>
-  <si>
     <t>Скорость робота</t>
   </si>
   <si>
-    <t>Состояние захвата 2</t>
-  </si>
-  <si>
     <t>Прижим при захвате детали с полки</t>
   </si>
   <si>
     <t>Прижим при установке деталь на полку</t>
   </si>
   <si>
-    <t>Состояние патрона 1</t>
-  </si>
-  <si>
     <t>Прижим при захвате детали из патрона</t>
   </si>
   <si>
     <t>Прижим при установке детали в патрон</t>
   </si>
   <si>
-    <t>Состояние патрона 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ожидание открытия кулачков патрона 1 после сигнала </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ожидание открытия кулачков патрона 2 после сигнала </t>
-  </si>
-  <si>
     <t>Обработано деталей</t>
   </si>
   <si>
-    <t xml:space="preserve">Ожидание закрытия кулачков патрона 1 после сигнала </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ожидание закрытия кулачков патрона 2 после сигнала </t>
-  </si>
-  <si>
     <t>Следующая деталь</t>
   </si>
   <si>
-    <t>Время открытия захвата 1</t>
-  </si>
-  <si>
-    <t>Время открытия захвата 2</t>
-  </si>
-  <si>
     <t>Код ошибки на роботе</t>
   </si>
   <si>
-    <t>Время закрытия захвата 1</t>
-  </si>
-  <si>
-    <t>Время закрытия захвата 2</t>
-  </si>
-  <si>
-    <t>Скорость поиска</t>
-  </si>
-  <si>
-    <t>Скоррость обдува</t>
-  </si>
-  <si>
-    <t>Обдув после забора детали</t>
-  </si>
-  <si>
-    <t>Обдув перед установкой детали</t>
-  </si>
-  <si>
-    <t>Сначала кулачки открывает станок</t>
-  </si>
-  <si>
-    <t>Реверс захвата 2</t>
-  </si>
-  <si>
-    <t>Реверс захвата 1</t>
-  </si>
-  <si>
-    <t>Из какого патрона забираем деталь</t>
-  </si>
-  <si>
-    <t>Каким захватом забираем деталь</t>
-  </si>
-  <si>
-    <t>В какой патрон ставим заготовку</t>
-  </si>
-  <si>
-    <t>Каким захватом берём заготовку</t>
-  </si>
-  <si>
-    <t>Количество деталей на полке</t>
-  </si>
-  <si>
-    <t>Смещение первого ряда относительно нуля Y</t>
-  </si>
-  <si>
-    <t>Смещение первого ряда относительно нуля Х</t>
-  </si>
-  <si>
     <t>Смещение чётного ряда</t>
   </si>
   <si>
@@ -384,49 +294,7 @@
     <t>Расстояние между рядами</t>
   </si>
   <si>
-    <t>Количество ячеек в чётных рядах пластины</t>
-  </si>
-  <si>
-    <t>Количество ячеек в нечётных рядах пластины</t>
-  </si>
-  <si>
     <t>Количество рядов на пластине</t>
-  </si>
-  <si>
-    <t>ID пластины в базе данных</t>
-  </si>
-  <si>
-    <t>Тело кулачков в Патроне 2</t>
-  </si>
-  <si>
-    <t>Высота кулачков в Патроне 2</t>
-  </si>
-  <si>
-    <t>Тело кулачков в Патроне 1</t>
-  </si>
-  <si>
-    <t>Высота кулачков в Патроне 1</t>
-  </si>
-  <si>
-    <t>Тело кулачков в захвате 2</t>
-  </si>
-  <si>
-    <t>Высота кулачков в захвате 2</t>
-  </si>
-  <si>
-    <t>Тело кулачков в захвате 1</t>
-  </si>
-  <si>
-    <t>Высота кулачков в захвате 1</t>
-  </si>
-  <si>
-    <t>Длина полуфабриката</t>
-  </si>
-  <si>
-    <t>Длина детали</t>
-  </si>
-  <si>
-    <t>Длина заготовки</t>
   </si>
   <si>
     <t>Переключение зоны безопасности на лидаре</t>
@@ -905,6 +773,114 @@
   </si>
   <si>
     <t>Поправка по высоте при развороте втулки</t>
+  </si>
+  <si>
+    <t>Состояние двойного захвата 1</t>
+  </si>
+  <si>
+    <t>Состояние двойного захвата 2</t>
+  </si>
+  <si>
+    <t>Состояние параллельного захвата</t>
+  </si>
+  <si>
+    <t>Состояние патрона</t>
+  </si>
+  <si>
+    <t>Состояние станции перехвата</t>
+  </si>
+  <si>
+    <t>Прижим при захвате детали из призмы</t>
+  </si>
+  <si>
+    <t>Прижим при установке детали в призмы</t>
+  </si>
+  <si>
+    <t>Время открытия двойного захвата 1</t>
+  </si>
+  <si>
+    <t>Время закрытия двойного захвата 1</t>
+  </si>
+  <si>
+    <t>Время открытия двойного захвата 2</t>
+  </si>
+  <si>
+    <t>Время закрытия двойного захвата 2</t>
+  </si>
+  <si>
+    <t>Время открытия параллельного захвата</t>
+  </si>
+  <si>
+    <t>Время закрытия параллельного захвата</t>
+  </si>
+  <si>
+    <t>Двойной захват. В захвате 1 заготовка</t>
+  </si>
+  <si>
+    <t>Двойной захват. В захвате 1 промежуточная деталь</t>
+  </si>
+  <si>
+    <t>Двойной захват. В захвате 1 готовая деталь</t>
+  </si>
+  <si>
+    <t>Двойной захват. В захвате 2 заготовка</t>
+  </si>
+  <si>
+    <t>Двойной захват. В захвате 2 промежуточная деталь</t>
+  </si>
+  <si>
+    <t>Двойной захват. В захвате 2 готовая деталь</t>
+  </si>
+  <si>
+    <t>Параллельный захват. В захвате заготовка</t>
+  </si>
+  <si>
+    <t>Параллельный захват. В захвате промежуточная деталь</t>
+  </si>
+  <si>
+    <t>Параллельный захват. В захвате готовая деталь</t>
+  </si>
+  <si>
+    <t>Патрон. В патроне заготовка</t>
+  </si>
+  <si>
+    <t>Патрон. В патроне промежуточная деталь</t>
+  </si>
+  <si>
+    <t>Патрон. В патроне готовая деталь</t>
+  </si>
+  <si>
+    <t>Станция перехвата. Заготовка</t>
+  </si>
+  <si>
+    <t>Станция перехвата. Промежуточная деталь</t>
+  </si>
+  <si>
+    <t>Двойной захват, захват 1, L1 (0)</t>
+  </si>
+  <si>
+    <t>Робот в режиме отладки</t>
+  </si>
+  <si>
+    <t>Двойной захват. Захват 1 пустой</t>
+  </si>
+  <si>
+    <t>Двойной захват. Захват 2 пустой</t>
+  </si>
+  <si>
+    <t>Параллельный захват. Захват пустой</t>
+  </si>
+  <si>
+    <t>Патрон. Пустой</t>
+  </si>
+  <si>
+    <t>Станция перехвата. Пустая</t>
+  </si>
+  <si>
+    <t>Номер задания</t>
+  </si>
+  <si>
+    <t>Количество заготовок</t>
   </si>
 </sst>
 </file>
@@ -969,7 +945,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -980,12 +956,6 @@
       <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1056,7 +1026,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1072,11 +1041,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1086,6 +1058,73 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1292,73 +1331,6 @@
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1373,52 +1345,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
   <autoFilter ref="A2:D898" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{01E43BCB-FF1F-49F0-8EDF-8BDB85A3A52E}" name="Адрес на роботе" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{E49880E5-7072-4525-BCB4-CE1A527AD7B0}" name="Программный адрес" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{01E43BCB-FF1F-49F0-8EDF-8BDB85A3A52E}" name="Адрес на роботе" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{E49880E5-7072-4525-BCB4-CE1A527AD7B0}" name="Программный адрес" dataDxfId="22">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(A3+65536-$A$3 +2*96, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6FB0113F-D5BD-4FC0-9B02-B55C66B93470}" name="Адрес слова" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{6FB0113F-D5BD-4FC0-9B02-B55C66B93470}" name="Адрес слова" dataDxfId="21">
       <calculatedColumnFormula>IF(RIGHT(B3,1)="0",LEFT(B3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4DE3B543-63F2-4F27-A542-D97E6805A269}" name="Комментарий" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{4DE3B543-63F2-4F27-A542-D97E6805A269}" name="Комментарий" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}" name="Таблица6" displayName="Таблица6" ref="F2:J898" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}" name="Таблица6" displayName="Таблица6" ref="F2:J898" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
   <autoFilter ref="F2:J898" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B59749FC-B984-4636-91DE-503B7E13DCCC}" name="Адрес на роботе" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{26D947D3-C6E7-42A6-80AF-4F5F45D689B5}" name="Программный адрес" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{B59749FC-B984-4636-91DE-503B7E13DCCC}" name="Адрес на роботе" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{26D947D3-C6E7-42A6-80AF-4F5F45D689B5}" name="Программный адрес" dataDxfId="15">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(F3+65536+4096 +2* 96-$F$3, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2A6702CA-A964-4A02-89A8-180932C37848}" name="Адрес слова" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{2A6702CA-A964-4A02-89A8-180932C37848}" name="Адрес слова" dataDxfId="14">
       <calculatedColumnFormula>IF(RIGHT(G3,1)="0",LEFT(G3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{14C27F77-1D34-48C7-8407-3A45CEFDA494}" name="Комментарий" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{892E34D9-9BCE-4F6E-9C33-9F094BD6773A}" name="Столбец1" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{14C27F77-1D34-48C7-8407-3A45CEFDA494}" name="Комментарий" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{892E34D9-9BCE-4F6E-9C33-9F094BD6773A}" name="Столбец1" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FBF9C563-851C-4C3E-9592-D9FFEC18338F}" name="Таблица3" displayName="Таблица3" ref="A1:H117" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
-  <autoFilter ref="A1:H117" xr:uid="{FBF9C563-851C-4C3E-9592-D9FFEC18338F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}" name="Таблица35" displayName="Таблица35" ref="A1:H117" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+  <autoFilter ref="A1:H117" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{57ACC912-6EA4-4565-94B4-FE0FABC2541E}" name="Физический адрес" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{A0CADD83-254E-4849-A201-5CB103F8E2EE}" name="Назначение" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{F49A2A83-4124-448A-9E06-CF2418852E09}" name="Комментарий" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{3D8A87D7-7D04-4B99-AA64-6767201F794F}" name="Нижний лимит" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{9C5119A3-3CBE-4270-AA72-A837AFB61283}" name="Верхний лимит" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{4E2FA42D-8C84-4CFC-B68B-6FA3F4B12F41}" name="Адрес на роботе" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{1D01C685-AD90-4A62-BFA3-062A4704149B}" name="Кол-во бит на роботе" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{35AAE794-90B2-4392-B591-CF52BD9AE5EC}" name="Преобразование" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{92D55AB5-DA85-4CE6-885A-51E3B1BAD618}" name="Физический адрес" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{74C09991-F50A-4EC3-9F41-CEBF1B9D9EBC}" name="Назначение" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{AE4EE521-2728-4FC7-BBC9-E3628F4E7893}" name="Комментарий" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4340E727-5C89-4710-A72C-D3D49E41FCE8}" name="Нижний лимит" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{7E71D017-2529-42CC-875C-F0DFB0A1764E}" name="Верхний лимит" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{EEC6976F-E174-47AA-A6ED-83856650B659}" name="Адрес на роботе" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{3A79B632-BB55-4ACF-9B1F-ABA093E90E2C}" name="Кол-во бит на роботе" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{8C0B7855-A039-4C8A-91C5-142421D6FEF0}" name="Преобразование" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1744,16 +1716,17 @@
   <dimension ref="A1:J898"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.109375" style="1"/>
-    <col min="6" max="6" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="6" max="6" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -2183,6 +2156,9 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="F16" s="1">
         <v>1078</v>
       </c>
@@ -2759,9 +2735,6 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="F38" s="1">
         <v>1100</v>
       </c>
@@ -2773,9 +2746,6 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -2789,9 +2759,6 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="F39" s="1">
         <v>1101</v>
       </c>
@@ -2803,9 +2770,6 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
@@ -3094,7 +3058,7 @@
         <v>P1003</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F51" s="1">
         <v>1113</v>
@@ -3108,7 +3072,7 @@
         <v>P1103</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
@@ -3124,7 +3088,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F52" s="1">
         <v>1114</v>
@@ -3134,7 +3098,7 @@
         <v>P11031</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -3150,7 +3114,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F53" s="1">
         <v>1115</v>
@@ -3177,7 +3141,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F54" s="1">
         <v>1116</v>
@@ -3204,7 +3168,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F55" s="1">
         <v>1117</v>
@@ -3231,7 +3195,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F56" s="1">
         <v>1118</v>
@@ -3258,7 +3222,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F57" s="1">
         <v>1119</v>
@@ -3285,7 +3249,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F58" s="1">
         <v>1120</v>
@@ -3504,7 +3468,7 @@
         <v>P1004</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F67" s="1">
         <v>1129</v>
@@ -3518,7 +3482,7 @@
         <v>P1104</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -3534,7 +3498,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F68" s="1">
         <v>1130</v>
@@ -3548,7 +3512,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
@@ -3564,7 +3528,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F69" s="1">
         <v>1131</v>
@@ -3578,7 +3542,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -3594,7 +3558,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F70" s="1">
         <v>1132</v>
@@ -3608,7 +3572,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
@@ -3624,7 +3588,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F71" s="1">
         <v>1133</v>
@@ -3638,7 +3602,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
@@ -3654,7 +3618,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F72" s="1">
         <v>1134</v>
@@ -3668,7 +3632,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
@@ -3684,7 +3648,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F73" s="1">
         <v>1135</v>
@@ -3698,7 +3662,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -3714,7 +3678,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F74" s="1">
         <v>1136</v>
@@ -3728,7 +3692,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -3755,7 +3719,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
@@ -3771,7 +3735,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F76" s="1">
         <v>1138</v>
@@ -3798,7 +3762,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F77" s="1">
         <v>1139</v>
@@ -3825,7 +3789,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F78" s="1">
         <v>1140</v>
@@ -3852,7 +3816,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F79" s="1">
         <v>1141</v>
@@ -3951,7 +3915,7 @@
         <v>P1005</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="F83" s="1">
         <v>1145</v>
@@ -4277,7 +4241,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>159</v>
       </c>
@@ -4301,7 +4265,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>160</v>
       </c>
@@ -4325,7 +4289,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>161</v>
       </c>
@@ -4337,19 +4301,22 @@
         <f t="shared" si="5"/>
         <v>P1006</v>
       </c>
-      <c r="F99" s="1">
-        <v>1161</v>
+      <c r="D99" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="G99" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P11060</v>
+        <v>P10BD7</v>
       </c>
       <c r="H99" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>P1106</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>162</v>
       </c>
@@ -4373,7 +4340,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>163</v>
       </c>
@@ -4397,7 +4364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>164</v>
       </c>
@@ -4421,7 +4388,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>165</v>
       </c>
@@ -4445,7 +4412,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>166</v>
       </c>
@@ -4469,7 +4436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>167</v>
       </c>
@@ -4493,7 +4460,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>168</v>
       </c>
@@ -4517,7 +4484,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>169</v>
       </c>
@@ -4541,7 +4508,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>170</v>
       </c>
@@ -4565,7 +4532,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>171</v>
       </c>
@@ -4589,7 +4556,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>172</v>
       </c>
@@ -4613,7 +4580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>173</v>
       </c>
@@ -4637,7 +4604,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>174</v>
       </c>
@@ -4661,7 +4628,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>175</v>
       </c>
@@ -4685,7 +4652,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>176</v>
       </c>
@@ -4709,7 +4676,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>177</v>
       </c>
@@ -4721,6 +4688,9 @@
         <f t="shared" si="5"/>
         <v>P1007</v>
       </c>
+      <c r="D115" s="1" t="s">
+        <v>246</v>
+      </c>
       <c r="F115" s="1">
         <v>1177</v>
       </c>
@@ -4732,8 +4702,11 @@
         <f t="shared" si="7"/>
         <v>P1107</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I115" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>178</v>
       </c>
@@ -4757,7 +4730,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>179</v>
       </c>
@@ -4781,7 +4754,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>180</v>
       </c>
@@ -4805,7 +4778,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>181</v>
       </c>
@@ -4829,7 +4802,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>182</v>
       </c>
@@ -4853,7 +4826,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>183</v>
       </c>
@@ -4877,7 +4850,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>184</v>
       </c>
@@ -4901,7 +4874,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>185</v>
       </c>
@@ -4924,8 +4897,11 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I123" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>186</v>
       </c>
@@ -4949,7 +4925,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>187</v>
       </c>
@@ -4973,7 +4949,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>188</v>
       </c>
@@ -4997,7 +4973,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>189</v>
       </c>
@@ -5021,7 +4997,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>190</v>
       </c>
@@ -5045,7 +5021,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>191</v>
       </c>
@@ -5069,7 +5045,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>192</v>
       </c>
@@ -5093,7 +5069,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>193</v>
       </c>
@@ -5105,6 +5081,9 @@
         <f t="shared" si="5"/>
         <v>P1008</v>
       </c>
+      <c r="D131" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="F131" s="1">
         <v>1193</v>
       </c>
@@ -5116,8 +5095,11 @@
         <f t="shared" si="7"/>
         <v>P1108</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I131" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>194</v>
       </c>
@@ -5141,7 +5123,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>195</v>
       </c>
@@ -5165,7 +5147,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>196</v>
       </c>
@@ -5189,7 +5171,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>197</v>
       </c>
@@ -5213,7 +5195,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>198</v>
       </c>
@@ -5237,7 +5219,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>199</v>
       </c>
@@ -5261,7 +5243,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>200</v>
       </c>
@@ -5285,7 +5267,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>201</v>
       </c>
@@ -5308,8 +5290,11 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I139" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>202</v>
       </c>
@@ -5333,7 +5318,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>203</v>
       </c>
@@ -5357,7 +5342,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>204</v>
       </c>
@@ -5381,7 +5366,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>205</v>
       </c>
@@ -5405,7 +5390,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>206</v>
       </c>
@@ -5429,7 +5414,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>207</v>
       </c>
@@ -5453,7 +5438,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>208</v>
       </c>
@@ -5477,7 +5462,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>209</v>
       </c>
@@ -5489,6 +5474,9 @@
         <f t="shared" si="9"/>
         <v>P1009</v>
       </c>
+      <c r="D147" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="F147" s="1">
         <v>1209</v>
       </c>
@@ -5500,8 +5488,11 @@
         <f t="shared" si="11"/>
         <v>P1109</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I147" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>210</v>
       </c>
@@ -5525,7 +5516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>211</v>
       </c>
@@ -5549,7 +5540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>212</v>
       </c>
@@ -5573,7 +5564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>213</v>
       </c>
@@ -5597,7 +5588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>214</v>
       </c>
@@ -5621,7 +5612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>215</v>
       </c>
@@ -5645,7 +5636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>216</v>
       </c>
@@ -5669,7 +5660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>217</v>
       </c>
@@ -5692,8 +5683,11 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I155" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>218</v>
       </c>
@@ -5717,7 +5711,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>219</v>
       </c>
@@ -5741,7 +5735,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>220</v>
       </c>
@@ -5765,7 +5759,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>221</v>
       </c>
@@ -5789,7 +5783,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>222</v>
       </c>
@@ -5874,7 +5868,7 @@
         <v>P1010</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="F163" s="1">
         <v>1225</v>
@@ -5888,7 +5882,7 @@
         <v>P1110</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>79</v>
+        <v>252</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -6082,6 +6076,9 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I171" s="1" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
@@ -6264,7 +6261,7 @@
         <v>P1011</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F179" s="1">
         <v>1241</v>
@@ -6278,7 +6275,7 @@
         <v>P1111</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>81</v>
+        <v>254</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -6473,7 +6470,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>82</v>
+        <v>255</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -6657,7 +6654,7 @@
         <v>P1012</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F195" s="1">
         <v>1257</v>
@@ -6671,7 +6668,7 @@
         <v>P1112</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>84</v>
+        <v>256</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
@@ -6866,7 +6863,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>85</v>
+        <v>257</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -7050,7 +7047,7 @@
         <v>P1013</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F211" s="1">
         <v>1273</v>
@@ -7064,7 +7061,7 @@
         <v>P1113</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>87</v>
+        <v>279</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
@@ -7259,7 +7256,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>88</v>
+        <v>280</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
@@ -7443,7 +7440,7 @@
         <v>P1014</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>89</v>
+        <v>274</v>
       </c>
       <c r="F227" s="1">
         <v>1289</v>
@@ -7456,8 +7453,8 @@
         <f t="shared" si="15"/>
         <v>P1114</v>
       </c>
-      <c r="I227" s="1" t="s">
-        <v>90</v>
+      <c r="I227" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
@@ -7472,6 +7469,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D228" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="F228" s="1">
         <v>1290</v>
       </c>
@@ -7483,6 +7483,9 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I228" s="6" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
@@ -7496,6 +7499,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D229" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="F229" s="1">
         <v>1291</v>
       </c>
@@ -7507,6 +7513,9 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I229" s="6" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
@@ -7520,6 +7529,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D230" s="1" t="s">
+        <v>260</v>
+      </c>
       <c r="F230" s="1">
         <v>1292</v>
       </c>
@@ -7531,6 +7543,9 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I230" s="6" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
@@ -7544,6 +7559,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D231" s="1" t="s">
+        <v>275</v>
+      </c>
       <c r="F231" s="1">
         <v>1293</v>
       </c>
@@ -7555,6 +7573,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I231" s="6"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
@@ -7568,6 +7587,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D232" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="F232" s="1">
         <v>1294</v>
       </c>
@@ -7579,6 +7601,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I232" s="6"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
@@ -7592,6 +7615,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D233" s="1" t="s">
+        <v>262</v>
+      </c>
       <c r="F233" s="1">
         <v>1295</v>
       </c>
@@ -7603,6 +7629,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I233" s="6"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
@@ -7616,6 +7643,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D234" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="F234" s="1">
         <v>1296</v>
       </c>
@@ -7627,6 +7657,9 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I234" s="6" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
@@ -7640,6 +7673,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D235" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="F235" s="1">
         <v>1297</v>
       </c>
@@ -7651,8 +7687,8 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I235" s="1" t="s">
-        <v>91</v>
+      <c r="I235" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
@@ -7667,6 +7703,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D236" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="F236" s="1">
         <v>1298</v>
       </c>
@@ -7678,6 +7717,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I236" s="6"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
@@ -7691,6 +7731,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D237" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="F237" s="1">
         <v>1299</v>
       </c>
@@ -7702,6 +7745,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I237" s="6"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
@@ -7715,6 +7759,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D238" s="1" t="s">
+        <v>266</v>
+      </c>
       <c r="F238" s="1">
         <v>1300</v>
       </c>
@@ -7726,6 +7773,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I238" s="6"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
@@ -7739,6 +7787,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D239" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="F239" s="1">
         <v>1301</v>
       </c>
@@ -7750,6 +7801,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I239" s="6"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
@@ -7763,6 +7815,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D240" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="F240" s="1">
         <v>1302</v>
       </c>
@@ -7774,6 +7829,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I240" s="6"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
@@ -7787,6 +7843,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D241" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="F241" s="1">
         <v>1303</v>
       </c>
@@ -7798,6 +7857,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I241" s="6"/>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
@@ -7811,6 +7871,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D242" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="F242" s="1">
         <v>1304</v>
       </c>
@@ -7836,7 +7899,7 @@
         <v>P1015</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>92</v>
+        <v>278</v>
       </c>
       <c r="F243" s="1">
         <v>1305</v>
@@ -7849,8 +7912,8 @@
         <f t="shared" si="15"/>
         <v>P1115</v>
       </c>
-      <c r="I243" s="1" t="s">
-        <v>93</v>
+      <c r="I243" s="6" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
@@ -7865,6 +7928,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D244" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="F244" s="1">
         <v>1306</v>
       </c>
@@ -7876,6 +7942,7 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I244" s="6"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
@@ -7889,6 +7956,9 @@
         <f t="shared" si="14"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="D245" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="F245" s="1">
         <v>1307</v>
       </c>
@@ -8044,9 +8114,6 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I251" s="1" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
@@ -8228,9 +8295,6 @@
         <f t="shared" si="14"/>
         <v>P1016</v>
       </c>
-      <c r="D259" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F259" s="1">
         <v>1321</v>
       </c>
@@ -8242,8 +8306,8 @@
         <f t="shared" si="15"/>
         <v>P1116</v>
       </c>
-      <c r="I259" s="1" t="s">
-        <v>96</v>
+      <c r="I259" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -8437,9 +8501,6 @@
         <f t="shared" si="19"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I267" s="1" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
@@ -8632,8 +8693,8 @@
         <f t="shared" si="19"/>
         <v>P1117</v>
       </c>
-      <c r="I275" s="1" t="s">
-        <v>98</v>
+      <c r="I275" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
@@ -8827,9 +8888,6 @@
         <f t="shared" si="19"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I283" s="1" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
@@ -8951,7 +9009,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>351</v>
       </c>
@@ -8975,7 +9033,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>352</v>
       </c>
@@ -8999,7 +9057,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>353</v>
       </c>
@@ -9022,8 +9080,11 @@
         <f t="shared" si="19"/>
         <v>P1118</v>
       </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I291" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>354</v>
       </c>
@@ -9047,7 +9108,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>355</v>
       </c>
@@ -9071,7 +9132,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>356</v>
       </c>
@@ -9095,7 +9156,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>357</v>
       </c>
@@ -9119,7 +9180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>358</v>
       </c>
@@ -9143,7 +9204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>359</v>
       </c>
@@ -9167,7 +9228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>360</v>
       </c>
@@ -9191,7 +9252,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>361</v>
       </c>
@@ -9215,7 +9276,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>362</v>
       </c>
@@ -9239,7 +9300,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>363</v>
       </c>
@@ -9263,7 +9324,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>364</v>
       </c>
@@ -9287,7 +9348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>365</v>
       </c>
@@ -9311,7 +9372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>366</v>
       </c>
@@ -9335,7 +9396,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>367</v>
       </c>
@@ -9359,7 +9420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>368</v>
       </c>
@@ -9383,7 +9444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>369</v>
       </c>
@@ -9406,8 +9467,11 @@
         <f t="shared" si="19"/>
         <v>P1119</v>
       </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I307" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>370</v>
       </c>
@@ -9431,7 +9495,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>371</v>
       </c>
@@ -9455,7 +9519,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>372</v>
       </c>
@@ -9479,7 +9543,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>373</v>
       </c>
@@ -9503,7 +9567,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>374</v>
       </c>
@@ -9527,7 +9591,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>375</v>
       </c>
@@ -9551,7 +9615,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>376</v>
       </c>
@@ -9575,7 +9639,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>377</v>
       </c>
@@ -9599,7 +9663,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>378</v>
       </c>
@@ -9623,7 +9687,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>379</v>
       </c>
@@ -9647,7 +9711,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>380</v>
       </c>
@@ -9671,7 +9735,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>381</v>
       </c>
@@ -9695,7 +9759,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>382</v>
       </c>
@@ -9719,7 +9783,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>383</v>
       </c>
@@ -9743,7 +9807,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>384</v>
       </c>
@@ -9767,7 +9831,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>385</v>
       </c>
@@ -9790,8 +9854,11 @@
         <f t="shared" si="19"/>
         <v>P1120</v>
       </c>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I323" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>386</v>
       </c>
@@ -9815,7 +9882,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>387</v>
       </c>
@@ -9839,7 +9906,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>388</v>
       </c>
@@ -9863,7 +9930,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>389</v>
       </c>
@@ -9887,7 +9954,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>390</v>
       </c>
@@ -9911,7 +9978,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>391</v>
       </c>
@@ -9935,7 +10002,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>392</v>
       </c>
@@ -9959,7 +10026,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>393</v>
       </c>
@@ -9983,7 +10050,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>394</v>
       </c>
@@ -10007,7 +10074,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>395</v>
       </c>
@@ -10031,7 +10098,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>396</v>
       </c>
@@ -10055,7 +10122,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>397</v>
       </c>
@@ -10079,7 +10146,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>398</v>
       </c>
@@ -10103,7 +10170,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>399</v>
       </c>
@@ -10127,7 +10194,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>400</v>
       </c>
@@ -10151,7 +10218,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>401</v>
       </c>
@@ -10174,8 +10241,11 @@
         <f t="shared" si="25"/>
         <v>P1121</v>
       </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I339" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>402</v>
       </c>
@@ -10199,7 +10269,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>403</v>
       </c>
@@ -10223,7 +10293,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>404</v>
       </c>
@@ -10247,7 +10317,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>405</v>
       </c>
@@ -10271,7 +10341,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>406</v>
       </c>
@@ -10295,7 +10365,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>407</v>
       </c>
@@ -10319,7 +10389,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>408</v>
       </c>
@@ -10343,7 +10413,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>409</v>
       </c>
@@ -10367,7 +10437,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>410</v>
       </c>
@@ -10391,7 +10461,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>411</v>
       </c>
@@ -10415,7 +10485,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>412</v>
       </c>
@@ -10439,7 +10509,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>413</v>
       </c>
@@ -10463,7 +10533,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>414</v>
       </c>
@@ -10487,7 +10557,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>415</v>
       </c>
@@ -10511,7 +10581,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>416</v>
       </c>
@@ -10535,7 +10605,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>417</v>
       </c>
@@ -10558,8 +10628,11 @@
         <f t="shared" si="25"/>
         <v>P1122</v>
       </c>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I355" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>418</v>
       </c>
@@ -10583,7 +10656,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>419</v>
       </c>
@@ -10607,7 +10680,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>420</v>
       </c>
@@ -10631,7 +10704,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>421</v>
       </c>
@@ -10655,7 +10728,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>422</v>
       </c>
@@ -10679,7 +10752,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>423</v>
       </c>
@@ -10703,7 +10776,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>424</v>
       </c>
@@ -10727,7 +10800,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>425</v>
       </c>
@@ -10751,7 +10824,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>426</v>
       </c>
@@ -10775,7 +10848,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>427</v>
       </c>
@@ -10799,7 +10872,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>428</v>
       </c>
@@ -10823,7 +10896,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>429</v>
       </c>
@@ -10847,7 +10920,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>430</v>
       </c>
@@ -10871,7 +10944,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>431</v>
       </c>
@@ -10895,7 +10968,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>432</v>
       </c>
@@ -10919,7 +10992,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>433</v>
       </c>
@@ -10942,8 +11015,11 @@
         <f t="shared" si="25"/>
         <v>P1123</v>
       </c>
-    </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I371" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>434</v>
       </c>
@@ -10967,7 +11043,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>435</v>
       </c>
@@ -10991,7 +11067,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>436</v>
       </c>
@@ -11015,7 +11091,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>437</v>
       </c>
@@ -11038,8 +11114,11 @@
         <f t="shared" si="25"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I375" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>438</v>
       </c>
@@ -11063,7 +11142,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>439</v>
       </c>
@@ -11087,7 +11166,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>440</v>
       </c>
@@ -11111,7 +11190,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>441</v>
       </c>
@@ -11134,8 +11213,11 @@
         <f t="shared" si="25"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I379" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>442</v>
       </c>
@@ -11159,7 +11241,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>443</v>
       </c>
@@ -11183,7 +11265,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>444</v>
       </c>
@@ -11207,7 +11289,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>445</v>
       </c>
@@ -11231,7 +11313,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>446</v>
       </c>
@@ -11255,7 +11337,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>447</v>
       </c>
@@ -11279,7 +11361,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>448</v>
       </c>
@@ -11303,7 +11385,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>449</v>
       </c>
@@ -11326,8 +11408,11 @@
         <f t="shared" si="25"/>
         <v>P1124</v>
       </c>
-    </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I387" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>450</v>
       </c>
@@ -11351,7 +11436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>451</v>
       </c>
@@ -11375,7 +11460,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>452</v>
       </c>
@@ -11399,7 +11484,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>453</v>
       </c>
@@ -11423,7 +11508,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>454</v>
       </c>
@@ -11447,7 +11532,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>455</v>
       </c>
@@ -11471,7 +11556,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>456</v>
       </c>
@@ -11495,7 +11580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>457</v>
       </c>
@@ -11519,7 +11604,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>458</v>
       </c>
@@ -11543,7 +11628,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>459</v>
       </c>
@@ -11567,7 +11652,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>460</v>
       </c>
@@ -11591,7 +11676,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>461</v>
       </c>
@@ -11615,7 +11700,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>462</v>
       </c>
@@ -11639,7 +11724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>463</v>
       </c>
@@ -11663,7 +11748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>464</v>
       </c>
@@ -11687,7 +11772,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>465</v>
       </c>
@@ -11710,8 +11795,11 @@
         <f t="shared" si="29"/>
         <v>P1125</v>
       </c>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I403" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>466</v>
       </c>
@@ -11735,7 +11823,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>467</v>
       </c>
@@ -11759,7 +11847,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>468</v>
       </c>
@@ -11783,7 +11871,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>469</v>
       </c>
@@ -11807,7 +11895,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>470</v>
       </c>
@@ -11831,7 +11919,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>471</v>
       </c>
@@ -11855,7 +11943,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>472</v>
       </c>
@@ -11879,7 +11967,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>473</v>
       </c>
@@ -11903,7 +11991,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>474</v>
       </c>
@@ -11927,7 +12015,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>475</v>
       </c>
@@ -11951,7 +12039,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>476</v>
       </c>
@@ -11975,7 +12063,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>477</v>
       </c>
@@ -11999,7 +12087,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>478</v>
       </c>
@@ -12023,7 +12111,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>479</v>
       </c>
@@ -12047,7 +12135,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>480</v>
       </c>
@@ -12071,7 +12159,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>481</v>
       </c>
@@ -12094,8 +12182,11 @@
         <f t="shared" si="29"/>
         <v>P1126</v>
       </c>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I419" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>482</v>
       </c>
@@ -12119,7 +12210,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>483</v>
       </c>
@@ -12143,7 +12234,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>484</v>
       </c>
@@ -12167,7 +12258,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>485</v>
       </c>
@@ -12191,7 +12282,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>486</v>
       </c>
@@ -12215,7 +12306,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>487</v>
       </c>
@@ -12239,7 +12330,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>488</v>
       </c>
@@ -12263,7 +12354,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>489</v>
       </c>
@@ -12287,7 +12378,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>490</v>
       </c>
@@ -12311,7 +12402,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>491</v>
       </c>
@@ -12335,7 +12426,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>492</v>
       </c>
@@ -12359,7 +12450,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>493</v>
       </c>
@@ -12383,7 +12474,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>494</v>
       </c>
@@ -12407,7 +12498,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>495</v>
       </c>
@@ -12431,7 +12522,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>496</v>
       </c>
@@ -12455,7 +12546,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>497</v>
       </c>
@@ -12478,8 +12569,11 @@
         <f t="shared" si="29"/>
         <v>P1127</v>
       </c>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I435" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>498</v>
       </c>
@@ -12503,7 +12597,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>499</v>
       </c>
@@ -12527,7 +12621,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>500</v>
       </c>
@@ -12551,7 +12645,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>501</v>
       </c>
@@ -12574,8 +12668,11 @@
         <f t="shared" si="29"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I439" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>502</v>
       </c>
@@ -12599,7 +12696,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>503</v>
       </c>
@@ -12623,7 +12720,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>504</v>
       </c>
@@ -12647,7 +12744,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>505</v>
       </c>
@@ -12670,8 +12767,11 @@
         <f t="shared" si="29"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I443" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>506</v>
       </c>
@@ -12695,7 +12795,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>507</v>
       </c>
@@ -12719,7 +12819,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>508</v>
       </c>
@@ -12743,7 +12843,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>509</v>
       </c>
@@ -12767,7 +12867,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>510</v>
       </c>
@@ -12791,7 +12891,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>511</v>
       </c>
@@ -12815,7 +12915,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>512</v>
       </c>
@@ -12839,7 +12939,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>513</v>
       </c>
@@ -12862,8 +12962,11 @@
         <f t="shared" si="29"/>
         <v>P1128</v>
       </c>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I451" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>514</v>
       </c>
@@ -12887,7 +12990,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>515</v>
       </c>
@@ -12911,7 +13014,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>516</v>
       </c>
@@ -12935,7 +13038,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>517</v>
       </c>
@@ -12959,7 +13062,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>518</v>
       </c>
@@ -12983,7 +13086,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>519</v>
       </c>
@@ -13007,7 +13110,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>520</v>
       </c>
@@ -13031,7 +13134,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>521</v>
       </c>
@@ -13055,7 +13158,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>522</v>
       </c>
@@ -13079,7 +13182,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>523</v>
       </c>
@@ -13103,7 +13206,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>524</v>
       </c>
@@ -13127,7 +13230,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>525</v>
       </c>
@@ -13151,7 +13254,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>526</v>
       </c>
@@ -13175,7 +13278,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>527</v>
       </c>
@@ -13199,7 +13302,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>528</v>
       </c>
@@ -13223,7 +13326,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>529</v>
       </c>
@@ -13246,8 +13349,11 @@
         <f t="shared" si="33"/>
         <v>P1129</v>
       </c>
-    </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I467" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>530</v>
       </c>
@@ -13271,7 +13377,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>531</v>
       </c>
@@ -13295,7 +13401,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>532</v>
       </c>
@@ -13319,7 +13425,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>533</v>
       </c>
@@ -13343,7 +13449,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>534</v>
       </c>
@@ -13367,7 +13473,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>535</v>
       </c>
@@ -13391,7 +13497,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>536</v>
       </c>
@@ -13415,7 +13521,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>537</v>
       </c>
@@ -13439,7 +13545,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>538</v>
       </c>
@@ -13463,7 +13569,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>539</v>
       </c>
@@ -13487,7 +13593,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>540</v>
       </c>
@@ -13511,7 +13617,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>541</v>
       </c>
@@ -13535,7 +13641,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>542</v>
       </c>
@@ -13559,7 +13665,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>543</v>
       </c>
@@ -13583,7 +13689,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>544</v>
       </c>
@@ -13607,7 +13713,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>545</v>
       </c>
@@ -13630,8 +13736,11 @@
         <f t="shared" si="33"/>
         <v>P1130</v>
       </c>
-    </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I483" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>546</v>
       </c>
@@ -13655,7 +13764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>547</v>
       </c>
@@ -13679,7 +13788,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>548</v>
       </c>
@@ -13703,7 +13812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>549</v>
       </c>
@@ -13727,7 +13836,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>550</v>
       </c>
@@ -13751,7 +13860,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>551</v>
       </c>
@@ -13775,7 +13884,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>552</v>
       </c>
@@ -13799,7 +13908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>553</v>
       </c>
@@ -13823,7 +13932,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>554</v>
       </c>
@@ -13847,7 +13956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>555</v>
       </c>
@@ -13871,7 +13980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>556</v>
       </c>
@@ -13895,7 +14004,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>557</v>
       </c>
@@ -13919,7 +14028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>558</v>
       </c>
@@ -13943,7 +14052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>559</v>
       </c>
@@ -13967,7 +14076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>560</v>
       </c>
@@ -13991,7 +14100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>561</v>
       </c>
@@ -14014,8 +14123,11 @@
         <f t="shared" si="33"/>
         <v>P1131</v>
       </c>
-    </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I499" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>562</v>
       </c>
@@ -14039,7 +14151,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>563</v>
       </c>
@@ -14063,7 +14175,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>564</v>
       </c>
@@ -14087,7 +14199,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>565</v>
       </c>
@@ -14111,7 +14223,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>566</v>
       </c>
@@ -14135,7 +14247,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>567</v>
       </c>
@@ -14159,7 +14271,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>568</v>
       </c>
@@ -14183,7 +14295,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>569</v>
       </c>
@@ -14207,7 +14319,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>570</v>
       </c>
@@ -14231,7 +14343,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>571</v>
       </c>
@@ -14255,7 +14367,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>572</v>
       </c>
@@ -14279,7 +14391,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>573</v>
       </c>
@@ -14303,7 +14415,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>574</v>
       </c>
@@ -14327,7 +14439,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>575</v>
       </c>
@@ -14351,7 +14463,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>576</v>
       </c>
@@ -14375,7 +14487,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>577</v>
       </c>
@@ -14398,8 +14510,11 @@
         <f t="shared" si="33"/>
         <v>P1132</v>
       </c>
-    </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I515" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>578</v>
       </c>
@@ -14423,7 +14538,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>579</v>
       </c>
@@ -14447,7 +14562,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>580</v>
       </c>
@@ -14471,7 +14586,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>581</v>
       </c>
@@ -14495,7 +14610,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>582</v>
       </c>
@@ -14519,7 +14634,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>583</v>
       </c>
@@ -14543,7 +14658,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>584</v>
       </c>
@@ -14567,7 +14682,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>585</v>
       </c>
@@ -14591,7 +14706,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>586</v>
       </c>
@@ -14615,7 +14730,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>587</v>
       </c>
@@ -14639,7 +14754,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>588</v>
       </c>
@@ -14663,7 +14778,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>589</v>
       </c>
@@ -14687,7 +14802,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>590</v>
       </c>
@@ -14711,7 +14826,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>591</v>
       </c>
@@ -14735,7 +14850,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>592</v>
       </c>
@@ -14759,7 +14874,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>593</v>
       </c>
@@ -14782,8 +14897,11 @@
         <f t="shared" si="37"/>
         <v>P1133</v>
       </c>
-    </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I531" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>594</v>
       </c>
@@ -14807,7 +14925,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>595</v>
       </c>
@@ -14831,7 +14949,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>596</v>
       </c>
@@ -14855,7 +14973,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>597</v>
       </c>
@@ -14879,7 +14997,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>598</v>
       </c>
@@ -14903,7 +15021,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>599</v>
       </c>
@@ -14927,7 +15045,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>600</v>
       </c>
@@ -14951,7 +15069,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>601</v>
       </c>
@@ -14975,7 +15093,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>602</v>
       </c>
@@ -14999,7 +15117,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>603</v>
       </c>
@@ -15023,7 +15141,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>604</v>
       </c>
@@ -15047,7 +15165,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>605</v>
       </c>
@@ -15071,7 +15189,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>606</v>
       </c>
@@ -15095,7 +15213,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>607</v>
       </c>
@@ -15119,7 +15237,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>608</v>
       </c>
@@ -15143,7 +15261,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>609</v>
       </c>
@@ -15166,8 +15284,11 @@
         <f t="shared" si="37"/>
         <v>P1134</v>
       </c>
-    </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I547" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>610</v>
       </c>
@@ -15191,7 +15312,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>611</v>
       </c>
@@ -15215,7 +15336,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>612</v>
       </c>
@@ -15239,7 +15360,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>613</v>
       </c>
@@ -15263,7 +15384,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>614</v>
       </c>
@@ -15287,7 +15408,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>615</v>
       </c>
@@ -15311,7 +15432,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>616</v>
       </c>
@@ -15335,7 +15456,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>617</v>
       </c>
@@ -15359,7 +15480,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>618</v>
       </c>
@@ -15383,7 +15504,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>619</v>
       </c>
@@ -15407,7 +15528,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>620</v>
       </c>
@@ -15431,7 +15552,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>621</v>
       </c>
@@ -15455,7 +15576,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>622</v>
       </c>
@@ -15479,7 +15600,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>623</v>
       </c>
@@ -15503,7 +15624,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>624</v>
       </c>
@@ -15527,7 +15648,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>625</v>
       </c>
@@ -15550,8 +15671,11 @@
         <f t="shared" si="37"/>
         <v>P1135</v>
       </c>
-    </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I563" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>626</v>
       </c>
@@ -15575,7 +15699,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>627</v>
       </c>
@@ -15599,7 +15723,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>628</v>
       </c>
@@ -15623,7 +15747,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>629</v>
       </c>
@@ -15647,7 +15771,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>630</v>
       </c>
@@ -15671,7 +15795,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>631</v>
       </c>
@@ -15695,7 +15819,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>632</v>
       </c>
@@ -15719,7 +15843,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>633</v>
       </c>
@@ -15743,7 +15867,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>634</v>
       </c>
@@ -15767,7 +15891,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>635</v>
       </c>
@@ -15791,7 +15915,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>636</v>
       </c>
@@ -15815,7 +15939,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>637</v>
       </c>
@@ -15839,7 +15963,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>638</v>
       </c>
@@ -15935,7 +16059,9 @@
         <f t="shared" si="37"/>
         <v>P1136</v>
       </c>
-      <c r="I579" s="3"/>
+      <c r="I579" s="6" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
@@ -16210,9 +16336,7 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I590" s="3" t="s">
-        <v>100</v>
-      </c>
+      <c r="I590" s="3"/>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
@@ -16237,9 +16361,7 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I591" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="I591" s="3"/>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
@@ -16264,11 +16386,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I592" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I592" s="3"/>
+    </row>
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>655</v>
       </c>
@@ -16291,11 +16411,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I593" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I593" s="3"/>
+    </row>
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>656</v>
       </c>
@@ -16318,11 +16436,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I594" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I594" s="3"/>
+    </row>
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>657</v>
       </c>
@@ -16345,11 +16461,11 @@
         <f t="shared" si="41"/>
         <v>P1137</v>
       </c>
-      <c r="I595" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I595" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>658</v>
       </c>
@@ -16372,8 +16488,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I596" s="3"/>
+    </row>
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>659</v>
       </c>
@@ -16396,11 +16513,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I597" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I597" s="3"/>
+    </row>
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>660</v>
       </c>
@@ -16423,8 +16538,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I598" s="3"/>
+    </row>
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>661</v>
       </c>
@@ -16447,14 +16563,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I599" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J599" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I599" s="3"/>
+    </row>
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>662</v>
       </c>
@@ -16477,8 +16588,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I600" s="3"/>
+    </row>
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>663</v>
       </c>
@@ -16501,14 +16613,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I601" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J601" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I601" s="3"/>
+    </row>
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>664</v>
       </c>
@@ -16531,8 +16638,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I602" s="3"/>
+    </row>
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>665</v>
       </c>
@@ -16555,11 +16663,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I603" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I603" s="3"/>
+    </row>
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>666</v>
       </c>
@@ -16582,8 +16688,9 @@
         <f t="shared" si="41"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I604" s="3"/>
+    </row>
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>667</v>
       </c>
@@ -16607,7 +16714,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>668</v>
       </c>
@@ -16631,7 +16738,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>669</v>
       </c>
@@ -16655,7 +16762,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>670</v>
       </c>
@@ -16750,8 +16857,8 @@
         <f t="shared" si="41"/>
         <v>P1138</v>
       </c>
-      <c r="I611" s="3" t="s">
-        <v>110</v>
+      <c r="I611" s="6" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.3">
@@ -17137,8 +17244,8 @@
         <f t="shared" si="41"/>
         <v>P1139</v>
       </c>
-      <c r="I627" s="3" t="s">
-        <v>111</v>
+      <c r="I627" s="6" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.3">
@@ -17524,8 +17631,8 @@
         <f t="shared" si="41"/>
         <v>P1140</v>
       </c>
-      <c r="I643" s="3" t="s">
-        <v>112</v>
+      <c r="I643" s="6" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.3">
@@ -17911,8 +18018,8 @@
         <f t="shared" si="47"/>
         <v>P1141</v>
       </c>
-      <c r="I659" s="3" t="s">
-        <v>113</v>
+      <c r="I659" s="6" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -18298,8 +18405,8 @@
         <f t="shared" si="47"/>
         <v>P1142</v>
       </c>
-      <c r="I675" s="3" t="s">
-        <v>114</v>
+      <c r="I675" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.3">
@@ -18685,8 +18792,8 @@
         <f t="shared" si="47"/>
         <v>P1143</v>
       </c>
-      <c r="I691" s="3" t="s">
-        <v>115</v>
+      <c r="I691" s="6" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.3">
@@ -18880,9 +18987,7 @@
         <f t="shared" si="47"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I699" s="3" t="s">
-        <v>116</v>
-      </c>
+      <c r="I699" s="3"/>
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
@@ -19075,9 +19180,7 @@
         <f t="shared" si="47"/>
         <v>P1144</v>
       </c>
-      <c r="I707" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="I707" s="3"/>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
@@ -19270,9 +19373,7 @@
         <f t="shared" si="51"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I715" s="3" t="s">
-        <v>118</v>
-      </c>
+      <c r="I715" s="3"/>
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
@@ -19465,9 +19566,7 @@
         <f t="shared" si="51"/>
         <v>P1145</v>
       </c>
-      <c r="I723" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="I723" s="3"/>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
@@ -19852,9 +19951,7 @@
         <f t="shared" si="51"/>
         <v>P1146</v>
       </c>
-      <c r="I739" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="I739" s="3"/>
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
@@ -20239,9 +20336,7 @@
         <f t="shared" si="51"/>
         <v>P1147</v>
       </c>
-      <c r="I755" s="3" t="s">
-        <v>121</v>
-      </c>
+      <c r="I755" s="3"/>
     </row>
     <row r="756" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
@@ -20626,9 +20721,7 @@
         <f t="shared" si="51"/>
         <v>P1148</v>
       </c>
-      <c r="I771" s="3" t="s">
-        <v>122</v>
-      </c>
+      <c r="I771" s="3"/>
     </row>
     <row r="772" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
@@ -21013,9 +21106,7 @@
         <f t="shared" si="55"/>
         <v>P1149</v>
       </c>
-      <c r="I787" s="3" t="s">
-        <v>123</v>
-      </c>
+      <c r="I787" s="3"/>
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
@@ -21400,9 +21491,7 @@
         <f t="shared" si="55"/>
         <v>P1150</v>
       </c>
-      <c r="I803" s="3" t="s">
-        <v>124</v>
-      </c>
+      <c r="I803" s="3"/>
     </row>
     <row r="804" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A804" s="1">
@@ -21787,9 +21876,7 @@
         <f t="shared" si="55"/>
         <v>P1151</v>
       </c>
-      <c r="I819" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="I819" s="3"/>
     </row>
     <row r="820" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A820" s="1">
@@ -22174,9 +22261,7 @@
         <f t="shared" si="55"/>
         <v>P1152</v>
       </c>
-      <c r="I835" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="I835" s="3"/>
     </row>
     <row r="836" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A836" s="1">
@@ -22561,9 +22646,7 @@
         <f t="shared" si="59"/>
         <v>P1153</v>
       </c>
-      <c r="I851" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="I851" s="3"/>
     </row>
     <row r="852" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A852" s="1">
@@ -22877,7 +22960,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A865" s="1">
         <v>927</v>
       </c>
@@ -22901,7 +22984,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A866" s="1">
         <v>928</v>
       </c>
@@ -22925,7 +23008,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A867" s="1">
         <v>929</v>
       </c>
@@ -22948,11 +23031,8 @@
         <f t="shared" si="59"/>
         <v>P1154</v>
       </c>
-      <c r="I867" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="868" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A868" s="1">
         <v>930</v>
       </c>
@@ -22976,7 +23056,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A869" s="1">
         <v>931</v>
       </c>
@@ -23000,7 +23080,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A870" s="1">
         <v>932</v>
       </c>
@@ -23024,7 +23104,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A871" s="1">
         <v>933</v>
       </c>
@@ -23048,7 +23128,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A872" s="1">
         <v>934</v>
       </c>
@@ -23072,7 +23152,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A873" s="1">
         <v>935</v>
       </c>
@@ -23096,7 +23176,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A874" s="1">
         <v>936</v>
       </c>
@@ -23120,7 +23200,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A875" s="1">
         <v>937</v>
       </c>
@@ -23144,7 +23224,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A876" s="1">
         <v>938</v>
       </c>
@@ -23168,7 +23248,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A877" s="1">
         <v>939</v>
       </c>
@@ -23192,7 +23272,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A878" s="1">
         <v>940</v>
       </c>
@@ -23216,7 +23296,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A879" s="1">
         <v>941</v>
       </c>
@@ -23240,7 +23320,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A880" s="1">
         <v>942</v>
       </c>
@@ -23264,7 +23344,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A881" s="1">
         <v>943</v>
       </c>
@@ -23288,7 +23368,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A882" s="1">
         <v>944</v>
       </c>
@@ -23312,7 +23392,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A883" s="1">
         <v>945</v>
       </c>
@@ -23335,11 +23415,8 @@
         <f t="shared" si="59"/>
         <v>P1155</v>
       </c>
-      <c r="I883" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="884" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A884" s="1">
         <v>946</v>
       </c>
@@ -23363,7 +23440,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A885" s="1">
         <v>947</v>
       </c>
@@ -23387,7 +23464,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A886" s="1">
         <v>948</v>
       </c>
@@ -23411,7 +23488,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A887" s="1">
         <v>949</v>
       </c>
@@ -23435,7 +23512,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A888" s="1">
         <v>950</v>
       </c>
@@ -23459,7 +23536,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A889" s="1">
         <v>951</v>
       </c>
@@ -23483,7 +23560,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A890" s="1">
         <v>952</v>
       </c>
@@ -23507,7 +23584,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A891" s="1">
         <v>953</v>
       </c>
@@ -23531,7 +23608,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A892" s="1">
         <v>954</v>
       </c>
@@ -23555,7 +23632,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A893" s="1">
         <v>955</v>
       </c>
@@ -23579,7 +23656,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A894" s="1">
         <v>956</v>
       </c>
@@ -23603,7 +23680,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A895" s="1">
         <v>957</v>
       </c>
@@ -23627,7 +23704,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A896" s="1">
         <v>958</v>
       </c>
@@ -23704,6 +23781,7 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="F1:I1"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
@@ -23728,1734 +23806,1816 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="1">
+        <v>1289</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="1">
+        <v>1290</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="1">
+        <v>1291</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="1">
+        <v>1296</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="1">
+        <v>1297</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10">
+        <v>250</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1305</v>
+      </c>
+      <c r="G18" s="6">
+        <v>16</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10">
+        <v>250</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1321</v>
+      </c>
+      <c r="G19" s="6">
+        <v>16</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="10">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10">
+        <v>250</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1337</v>
+      </c>
+      <c r="G20" s="6">
+        <v>16</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="10">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10">
+        <v>250</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1353</v>
+      </c>
+      <c r="G21" s="6">
+        <v>16</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10">
+        <v>250</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1369</v>
+      </c>
+      <c r="G22" s="6">
+        <v>16</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
+        <v>250</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1385</v>
+      </c>
+      <c r="G23" s="6">
+        <v>16</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="10">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10">
+        <v>250</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1401</v>
+      </c>
+      <c r="G24" s="6">
+        <v>16</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="10">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10">
+        <v>250</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1417</v>
+      </c>
+      <c r="G25" s="6">
+        <v>16</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6">
+        <v>15</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1433</v>
+      </c>
+      <c r="G27" s="6">
+        <v>4</v>
+      </c>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>15</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1437</v>
+      </c>
+      <c r="G28" s="6">
+        <v>4</v>
+      </c>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>15</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1441</v>
+      </c>
+      <c r="G29" s="6">
+        <v>4</v>
+      </c>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6">
+        <v>800</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1449</v>
+      </c>
+      <c r="G30" s="6">
+        <v>16</v>
+      </c>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6">
+        <v>800</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1465</v>
+      </c>
+      <c r="G31" s="6">
+        <v>16</v>
+      </c>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
+        <v>800</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1481</v>
+      </c>
+      <c r="G32" s="6">
+        <v>16</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1497</v>
+      </c>
+      <c r="G34" s="6">
+        <v>4</v>
+      </c>
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6">
+        <v>4</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1501</v>
+      </c>
+      <c r="G35" s="6">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6">
+        <v>50</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1505</v>
+      </c>
+      <c r="G36" s="6">
+        <v>4</v>
+      </c>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="10">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10">
+        <v>250</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1513</v>
+      </c>
+      <c r="G38" s="6">
+        <v>16</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="10">
+        <v>1</v>
+      </c>
+      <c r="E39" s="10">
+        <v>250</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1737</v>
+      </c>
+      <c r="G39" s="6">
+        <v>16</v>
+      </c>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="10">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10">
+        <v>250</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1529</v>
+      </c>
+      <c r="G40" s="6">
+        <v>16</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="10">
+        <v>1</v>
+      </c>
+      <c r="E41" s="10">
+        <v>250</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1753</v>
+      </c>
+      <c r="G41" s="6">
+        <v>16</v>
+      </c>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="10">
+        <v>1</v>
+      </c>
+      <c r="E43" s="10">
+        <v>250</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1545</v>
+      </c>
+      <c r="G43" s="6">
+        <v>16</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="10">
+        <v>1</v>
+      </c>
+      <c r="E44" s="10">
+        <v>250</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1561</v>
+      </c>
+      <c r="G44" s="6">
+        <v>16</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="10">
+        <v>1</v>
+      </c>
+      <c r="E45" s="10">
+        <v>99</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1577</v>
+      </c>
+      <c r="G45" s="6">
+        <v>16</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="10">
+        <v>1</v>
+      </c>
+      <c r="E46" s="10">
+        <v>250</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1593</v>
+      </c>
+      <c r="G46" s="6">
+        <v>16</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="10">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10">
+        <v>250</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1609</v>
+      </c>
+      <c r="G47" s="6">
+        <v>16</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="10">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10">
+        <v>250</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1625</v>
+      </c>
+      <c r="G48" s="6">
+        <v>16</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="10">
+        <v>1</v>
+      </c>
+      <c r="E49" s="10">
+        <v>250</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1641</v>
+      </c>
+      <c r="G49" s="6">
+        <v>16</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="10">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10">
+        <v>99</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1657</v>
+      </c>
+      <c r="G50" s="6">
+        <v>16</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="10">
+        <v>1</v>
+      </c>
+      <c r="E51" s="10">
+        <v>250</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1673</v>
+      </c>
+      <c r="G51" s="6">
+        <v>16</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="10">
+        <v>1</v>
+      </c>
+      <c r="E52" s="10">
+        <v>250</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1689</v>
+      </c>
+      <c r="G52" s="6">
+        <v>16</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6">
+        <v>5</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1705</v>
+      </c>
+      <c r="G54" s="6">
+        <v>4</v>
+      </c>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6">
+        <v>0</v>
+      </c>
+      <c r="E55" s="6">
+        <v>50</v>
+      </c>
+      <c r="F55" s="1">
+        <v>1721</v>
+      </c>
+      <c r="G55" s="6">
+        <v>8</v>
+      </c>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="11">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11">
-        <v>250</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7">
-        <v>16</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="11">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11">
-        <v>250</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7">
-        <v>16</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="11">
-        <v>1</v>
-      </c>
-      <c r="E20" s="11">
-        <v>250</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7">
-        <v>16</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="11">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11">
-        <v>250</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7">
-        <v>16</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="11">
-        <v>1</v>
-      </c>
-      <c r="E22" s="11">
-        <v>250</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7">
-        <v>16</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="11">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11">
-        <v>250</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7">
-        <v>16</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="11">
-        <v>1</v>
-      </c>
-      <c r="E24" s="11">
-        <v>250</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7">
-        <v>16</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="11">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11">
-        <v>250</v>
-      </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7">
-        <v>16</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7">
-        <v>1</v>
-      </c>
-      <c r="E27" s="7">
-        <v>15</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7">
-        <v>4</v>
-      </c>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7">
-        <v>15</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7">
-        <v>4</v>
-      </c>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7">
-        <v>1</v>
-      </c>
-      <c r="E29" s="7">
-        <v>15</v>
-      </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7">
-        <v>4</v>
-      </c>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7">
-        <v>800</v>
-      </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7">
-        <v>16</v>
-      </c>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7">
-        <v>800</v>
-      </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7">
-        <v>16</v>
-      </c>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7">
-        <v>800</v>
-      </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7">
-        <v>16</v>
-      </c>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7">
-        <v>8</v>
-      </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7">
-        <v>1</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4</v>
-      </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7">
-        <v>50</v>
-      </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="11">
-        <v>1</v>
-      </c>
-      <c r="E38" s="11">
-        <v>250</v>
-      </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7">
-        <v>16</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="11">
-        <v>1</v>
-      </c>
-      <c r="E39" s="11">
-        <v>250</v>
-      </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7">
-        <v>16</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="11">
-        <v>1</v>
-      </c>
-      <c r="E40" s="11">
-        <v>250</v>
-      </c>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7">
-        <v>16</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="11">
-        <v>1</v>
-      </c>
-      <c r="E41" s="11">
-        <v>250</v>
-      </c>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7">
-        <v>16</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="11">
-        <v>1</v>
-      </c>
-      <c r="E43" s="11">
-        <v>250</v>
-      </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7">
-        <v>16</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="11">
-        <v>1</v>
-      </c>
-      <c r="E44" s="11">
-        <v>250</v>
-      </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7">
-        <v>16</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="11">
-        <v>1</v>
-      </c>
-      <c r="E45" s="11">
-        <v>99</v>
-      </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7">
-        <v>8</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="11">
-        <v>1</v>
-      </c>
-      <c r="E46" s="11">
-        <v>250</v>
-      </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7">
-        <v>16</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="11">
-        <v>1</v>
-      </c>
-      <c r="E47" s="11">
-        <v>250</v>
-      </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7">
-        <v>16</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="11">
-        <v>1</v>
-      </c>
-      <c r="E48" s="11">
-        <v>250</v>
-      </c>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7">
-        <v>16</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="11">
-        <v>1</v>
-      </c>
-      <c r="E49" s="11">
-        <v>250</v>
-      </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7">
-        <v>16</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="11">
-        <v>1</v>
-      </c>
-      <c r="E50" s="11">
-        <v>99</v>
-      </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7">
-        <v>8</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="11">
-        <v>1</v>
-      </c>
-      <c r="E51" s="11">
-        <v>250</v>
-      </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7">
-        <v>16</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="11">
-        <v>1</v>
-      </c>
-      <c r="E52" s="11">
-        <v>250</v>
-      </c>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7">
-        <v>16</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7">
-        <v>1</v>
-      </c>
-      <c r="E54" s="7">
-        <v>5</v>
-      </c>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7">
-        <v>0</v>
-      </c>
-      <c r="E55" s="7">
-        <v>50</v>
-      </c>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="s">
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="11"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="s">
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="7" t="s">
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="11"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="s">
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="11"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="6"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="6"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="11"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
+      <c r="B117" s="6"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="11"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DB\Projects\SW002-LoadWizardPro_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBF0D35-DEFC-4BF8-8BD5-93CCA22F1E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DBCE76-E1A7-49F8-AA08-8F51EE97073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Robot FieldBus" sheetId="1" r:id="rId1"/>
@@ -12767,9 +12767,6 @@
         <f t="shared" si="29"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I443" s="6" t="s">
-        <v>226</v>
-      </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
@@ -19180,7 +19177,9 @@
         <f t="shared" si="47"/>
         <v>P1144</v>
       </c>
-      <c r="I707" s="3"/>
+      <c r="I707" s="6" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
@@ -24454,10 +24453,10 @@
         <v>50</v>
       </c>
       <c r="F36" s="1">
-        <v>1505</v>
+        <v>1769</v>
       </c>
       <c r="G36" s="6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H36" s="6"/>
     </row>

--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DB\Projects\SW002-LoadWizardPro_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DBCE76-E1A7-49F8-AA08-8F51EE97073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D403CEE-FF37-4285-8097-E4069CEE7935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
+    <workbookView xWindow="10068" yWindow="792" windowWidth="17280" windowHeight="8880" tabRatio="607" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Robot FieldBus" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="283">
   <si>
     <t>Сигналы от Робота к ПЛК</t>
   </si>
@@ -262,18 +262,6 @@
   </si>
   <si>
     <t>Скорость робота</t>
-  </si>
-  <si>
-    <t>Прижим при захвате детали с полки</t>
-  </si>
-  <si>
-    <t>Прижим при установке деталь на полку</t>
-  </si>
-  <si>
-    <t>Прижим при захвате детали из патрона</t>
-  </si>
-  <si>
-    <t>Прижим при установке детали в патрон</t>
   </si>
   <si>
     <t>Обработано деталей</t>
@@ -790,12 +778,6 @@
     <t>Состояние станции перехвата</t>
   </si>
   <si>
-    <t>Прижим при захвате детали из призмы</t>
-  </si>
-  <si>
-    <t>Прижим при установке детали в призмы</t>
-  </si>
-  <si>
     <t>Время открытия двойного захвата 1</t>
   </si>
   <si>
@@ -881,6 +863,30 @@
   </si>
   <si>
     <t>Количество заготовок</t>
+  </si>
+  <si>
+    <t>Двойной захват, кулачки 2 работают на разжим</t>
+  </si>
+  <si>
+    <t>Двойной захват, захват 1, L3</t>
+  </si>
+  <si>
+    <t>Двойной захват, захват 1, l3</t>
+  </si>
+  <si>
+    <t>Прижим для полки</t>
+  </si>
+  <si>
+    <t>Прижим для станка</t>
+  </si>
+  <si>
+    <t>Прижим для перехвата</t>
+  </si>
+  <si>
+    <t>Робота в домашнее положение</t>
+  </si>
+  <si>
+    <t>Сначала зажимается патрон, потом открывается захват</t>
   </si>
 </sst>
 </file>
@@ -1058,73 +1064,6 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1331,6 +1270,73 @@
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1345,52 +1351,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:D898" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{01E43BCB-FF1F-49F0-8EDF-8BDB85A3A52E}" name="Адрес на роботе" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{E49880E5-7072-4525-BCB4-CE1A527AD7B0}" name="Программный адрес" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{01E43BCB-FF1F-49F0-8EDF-8BDB85A3A52E}" name="Адрес на роботе" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{E49880E5-7072-4525-BCB4-CE1A527AD7B0}" name="Программный адрес" dataDxfId="10">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(A3+65536-$A$3 +2*96, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6FB0113F-D5BD-4FC0-9B02-B55C66B93470}" name="Адрес слова" dataDxfId="21">
+    <tableColumn id="3" xr3:uid="{6FB0113F-D5BD-4FC0-9B02-B55C66B93470}" name="Адрес слова" dataDxfId="9">
       <calculatedColumnFormula>IF(RIGHT(B3,1)="0",LEFT(B3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4DE3B543-63F2-4F27-A542-D97E6805A269}" name="Комментарий" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{4DE3B543-63F2-4F27-A542-D97E6805A269}" name="Комментарий" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}" name="Таблица6" displayName="Таблица6" ref="F2:J898" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}" name="Таблица6" displayName="Таблица6" ref="F2:J898" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="F2:J898" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B59749FC-B984-4636-91DE-503B7E13DCCC}" name="Адрес на роботе" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{26D947D3-C6E7-42A6-80AF-4F5F45D689B5}" name="Программный адрес" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{B59749FC-B984-4636-91DE-503B7E13DCCC}" name="Адрес на роботе" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{26D947D3-C6E7-42A6-80AF-4F5F45D689B5}" name="Программный адрес" dataDxfId="3">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(F3+65536+4096 +2* 96-$F$3, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2A6702CA-A964-4A02-89A8-180932C37848}" name="Адрес слова" dataDxfId="14">
+    <tableColumn id="3" xr3:uid="{2A6702CA-A964-4A02-89A8-180932C37848}" name="Адрес слова" dataDxfId="2">
       <calculatedColumnFormula>IF(RIGHT(G3,1)="0",LEFT(G3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{14C27F77-1D34-48C7-8407-3A45CEFDA494}" name="Комментарий" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{892E34D9-9BCE-4F6E-9C33-9F094BD6773A}" name="Столбец1" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{14C27F77-1D34-48C7-8407-3A45CEFDA494}" name="Комментарий" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{892E34D9-9BCE-4F6E-9C33-9F094BD6773A}" name="Столбец1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}" name="Таблица35" displayName="Таблица35" ref="A1:H117" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}" name="Таблица35" displayName="Таблица35" ref="A1:H117" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
   <autoFilter ref="A1:H117" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{92D55AB5-DA85-4CE6-885A-51E3B1BAD618}" name="Физический адрес" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{74C09991-F50A-4EC3-9F41-CEBF1B9D9EBC}" name="Назначение" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{AE4EE521-2728-4FC7-BBC9-E3628F4E7893}" name="Комментарий" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{4340E727-5C89-4710-A72C-D3D49E41FCE8}" name="Нижний лимит" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{7E71D017-2529-42CC-875C-F0DFB0A1764E}" name="Верхний лимит" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{EEC6976F-E174-47AA-A6ED-83856650B659}" name="Адрес на роботе" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{3A79B632-BB55-4ACF-9B1F-ABA093E90E2C}" name="Кол-во бит на роботе" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{8C0B7855-A039-4C8A-91C5-142421D6FEF0}" name="Преобразование" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{92D55AB5-DA85-4CE6-885A-51E3B1BAD618}" name="Физический адрес" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{74C09991-F50A-4EC3-9F41-CEBF1B9D9EBC}" name="Назначение" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{AE4EE521-2728-4FC7-BBC9-E3628F4E7893}" name="Комментарий" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{4340E727-5C89-4710-A72C-D3D49E41FCE8}" name="Нижний лимит" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{7E71D017-2529-42CC-875C-F0DFB0A1764E}" name="Верхний лимит" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{EEC6976F-E174-47AA-A6ED-83856650B659}" name="Адрес на роботе" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{3A79B632-BB55-4ACF-9B1F-ABA093E90E2C}" name="Кол-во бит на роботе" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{8C0B7855-A039-4C8A-91C5-142421D6FEF0}" name="Преобразование" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2157,7 +2163,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F16" s="1">
         <v>1078</v>
@@ -3127,6 +3133,9 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
+      <c r="I53" s="1" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
@@ -3915,7 +3924,7 @@
         <v>P1005</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F83" s="1">
         <v>1145</v>
@@ -4302,15 +4311,18 @@
         <v>P1006</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
+      </c>
+      <c r="F99" s="1">
+        <v>1161</v>
       </c>
       <c r="G99" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P10BD7</v>
+        <v>P11060</v>
       </c>
       <c r="H99" s="1" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve"> </v>
+        <v>P1106</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>74</v>
@@ -4689,7 +4701,7 @@
         <v>P1007</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F115" s="1">
         <v>1177</v>
@@ -4703,7 +4715,7 @@
         <v>P1107</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>75</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
@@ -4897,9 +4909,6 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I123" s="1" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
@@ -5082,7 +5091,7 @@
         <v>P1008</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F131" s="1">
         <v>1193</v>
@@ -5096,7 +5105,7 @@
         <v>P1108</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>77</v>
+        <v>279</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
@@ -5290,9 +5299,6 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I139" s="1" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
@@ -5475,7 +5481,7 @@
         <v>P1009</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F147" s="1">
         <v>1209</v>
@@ -5489,7 +5495,7 @@
         <v>P1109</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
@@ -5683,9 +5689,6 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I155" s="1" t="s">
-        <v>250</v>
-      </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
@@ -5868,7 +5871,7 @@
         <v>P1010</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F163" s="1">
         <v>1225</v>
@@ -5882,7 +5885,7 @@
         <v>P1110</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -6077,7 +6080,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
@@ -6261,7 +6264,7 @@
         <v>P1011</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F179" s="1">
         <v>1241</v>
@@ -6275,7 +6278,7 @@
         <v>P1111</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -6470,7 +6473,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -6654,7 +6657,7 @@
         <v>P1012</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F195" s="1">
         <v>1257</v>
@@ -6668,7 +6671,7 @@
         <v>P1112</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
@@ -6863,7 +6866,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -7047,7 +7050,7 @@
         <v>P1013</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F211" s="1">
         <v>1273</v>
@@ -7061,7 +7064,7 @@
         <v>P1113</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
@@ -7256,7 +7259,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
@@ -7440,7 +7443,7 @@
         <v>P1014</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F227" s="1">
         <v>1289</v>
@@ -7454,7 +7457,7 @@
         <v>P1114</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
@@ -7470,7 +7473,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F228" s="1">
         <v>1290</v>
@@ -7484,7 +7487,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
@@ -7500,7 +7503,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F229" s="1">
         <v>1291</v>
@@ -7514,7 +7517,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I229" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
@@ -7530,7 +7533,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F230" s="1">
         <v>1292</v>
@@ -7544,7 +7547,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I230" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
@@ -7560,7 +7563,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F231" s="1">
         <v>1293</v>
@@ -7588,7 +7591,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F232" s="1">
         <v>1294</v>
@@ -7616,7 +7619,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F233" s="1">
         <v>1295</v>
@@ -7644,7 +7647,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F234" s="1">
         <v>1296</v>
@@ -7658,7 +7661,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
@@ -7674,7 +7677,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F235" s="1">
         <v>1297</v>
@@ -7688,7 +7691,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
@@ -7704,7 +7707,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F236" s="1">
         <v>1298</v>
@@ -7717,7 +7720,9 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I236" s="6"/>
+      <c r="I236" s="6" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
@@ -7732,7 +7737,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F237" s="1">
         <v>1299</v>
@@ -7760,7 +7765,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F238" s="1">
         <v>1300</v>
@@ -7788,7 +7793,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F239" s="1">
         <v>1301</v>
@@ -7816,7 +7821,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F240" s="1">
         <v>1302</v>
@@ -7844,7 +7849,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F241" s="1">
         <v>1303</v>
@@ -7872,7 +7877,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="F242" s="1">
         <v>1304</v>
@@ -7899,7 +7904,7 @@
         <v>P1015</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F243" s="1">
         <v>1305</v>
@@ -7913,7 +7918,7 @@
         <v>P1115</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
@@ -7929,7 +7934,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F244" s="1">
         <v>1306</v>
@@ -7957,7 +7962,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F245" s="1">
         <v>1307</v>
@@ -8307,7 +8312,7 @@
         <v>P1116</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -8694,7 +8699,7 @@
         <v>P1117</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
@@ -9081,7 +9086,7 @@
         <v>P1118</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
@@ -9468,7 +9473,7 @@
         <v>P1119</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
@@ -9855,7 +9860,7 @@
         <v>P1120</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
@@ -10242,7 +10247,7 @@
         <v>P1121</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.3">
@@ -10629,7 +10634,7 @@
         <v>P1122</v>
       </c>
       <c r="I355" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
@@ -11016,7 +11021,7 @@
         <v>P1123</v>
       </c>
       <c r="I371" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
@@ -11115,7 +11120,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I375" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
@@ -11214,7 +11219,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I379" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
@@ -11409,7 +11414,7 @@
         <v>P1124</v>
       </c>
       <c r="I387" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.3">
@@ -11796,7 +11801,7 @@
         <v>P1125</v>
       </c>
       <c r="I403" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
@@ -12183,7 +12188,7 @@
         <v>P1126</v>
       </c>
       <c r="I419" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.3">
@@ -12570,7 +12575,7 @@
         <v>P1127</v>
       </c>
       <c r="I435" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
@@ -12669,7 +12674,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I439" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.3">
@@ -12960,7 +12965,7 @@
         <v>P1128</v>
       </c>
       <c r="I451" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
@@ -13347,7 +13352,7 @@
         <v>P1129</v>
       </c>
       <c r="I467" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.3">
@@ -13734,7 +13739,7 @@
         <v>P1130</v>
       </c>
       <c r="I483" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.3">
@@ -14121,7 +14126,7 @@
         <v>P1131</v>
       </c>
       <c r="I499" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.3">
@@ -14508,7 +14513,7 @@
         <v>P1132</v>
       </c>
       <c r="I515" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.3">
@@ -14895,7 +14900,7 @@
         <v>P1133</v>
       </c>
       <c r="I531" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.3">
@@ -15282,7 +15287,7 @@
         <v>P1134</v>
       </c>
       <c r="I547" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.3">
@@ -15669,7 +15674,7 @@
         <v>P1135</v>
       </c>
       <c r="I563" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.3">
@@ -16057,7 +16062,7 @@
         <v>P1136</v>
       </c>
       <c r="I579" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.3">
@@ -16459,7 +16464,7 @@
         <v>P1137</v>
       </c>
       <c r="I595" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.3">
@@ -16855,7 +16860,7 @@
         <v>P1138</v>
       </c>
       <c r="I611" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.3">
@@ -17242,7 +17247,7 @@
         <v>P1139</v>
       </c>
       <c r="I627" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.3">
@@ -17629,7 +17634,7 @@
         <v>P1140</v>
       </c>
       <c r="I643" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.3">
@@ -18016,7 +18021,7 @@
         <v>P1141</v>
       </c>
       <c r="I659" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -18403,7 +18408,7 @@
         <v>P1142</v>
       </c>
       <c r="I675" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.3">
@@ -18790,7 +18795,7 @@
         <v>P1143</v>
       </c>
       <c r="I691" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.3">
@@ -19178,7 +19183,7 @@
         <v>P1144</v>
       </c>
       <c r="I707" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.3">
@@ -19565,7 +19570,9 @@
         <f t="shared" si="51"/>
         <v>P1145</v>
       </c>
-      <c r="I723" s="3"/>
+      <c r="I723" s="6" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
@@ -19950,7 +19957,9 @@
         <f t="shared" si="51"/>
         <v>P1146</v>
       </c>
-      <c r="I739" s="3"/>
+      <c r="I739" s="6" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
@@ -23806,52 +23815,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="7"/>
-      <c r="F2" s="11"/>
+      <c r="F2" s="1">
+        <v>1292</v>
+      </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -23864,10 +23875,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -23880,10 +23891,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -23896,7 +23907,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -23908,7 +23919,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -23920,7 +23931,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -23932,7 +23943,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -23944,10 +23955,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -23960,10 +23971,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -23976,19 +23987,23 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="6"/>
+        <v>195</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>282</v>
+      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="11"/>
+      <c r="F12" s="11">
+        <v>1298</v>
+      </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -24000,7 +24015,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -24012,7 +24027,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -24024,7 +24039,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -24036,7 +24051,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -24048,10 +24063,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="10">
@@ -24067,15 +24082,15 @@
         <v>16</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="10">
@@ -24091,15 +24106,15 @@
         <v>16</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="10">
@@ -24115,15 +24130,15 @@
         <v>16</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="10">
@@ -24139,15 +24154,15 @@
         <v>16</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="10">
@@ -24163,15 +24178,15 @@
         <v>16</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="10">
@@ -24187,15 +24202,15 @@
         <v>16</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="10">
@@ -24211,15 +24226,15 @@
         <v>16</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="10">
@@ -24235,12 +24250,12 @@
         <v>16</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -24252,10 +24267,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6">
@@ -24274,10 +24289,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6">
@@ -24296,10 +24311,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6">
@@ -24318,10 +24333,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6">
@@ -24340,10 +24355,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6">
@@ -24362,10 +24377,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6">
@@ -24384,7 +24399,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -24396,10 +24411,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6">
@@ -24418,10 +24433,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6">
@@ -24440,10 +24455,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="6">
@@ -24462,7 +24477,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -24474,10 +24489,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="10">
@@ -24493,15 +24508,15 @@
         <v>16</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="10">
@@ -24520,10 +24535,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="10">
@@ -24539,15 +24554,15 @@
         <v>16</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="10">
@@ -24566,7 +24581,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -24578,10 +24593,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="10">
@@ -24597,15 +24612,15 @@
         <v>16</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="10">
@@ -24621,15 +24636,15 @@
         <v>16</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="10">
@@ -24645,15 +24660,15 @@
         <v>16</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="10">
@@ -24669,15 +24684,15 @@
         <v>16</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="10">
@@ -24693,15 +24708,15 @@
         <v>16</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="10">
@@ -24717,15 +24732,15 @@
         <v>16</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="10">
@@ -24741,15 +24756,15 @@
         <v>16</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="10">
@@ -24765,15 +24780,15 @@
         <v>16</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="10">
@@ -24789,15 +24804,15 @@
         <v>16</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="10">
@@ -24813,12 +24828,12 @@
         <v>16</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -24830,10 +24845,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="6">
@@ -24852,10 +24867,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C55" s="6"/>
       <c r="D55" s="6">
@@ -24874,31 +24889,55 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B56" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>276</v>
+      </c>
       <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
+      <c r="D56" s="10">
+        <v>1</v>
+      </c>
+      <c r="E56" s="10">
+        <v>250</v>
+      </c>
+      <c r="F56" s="1">
+        <v>1785</v>
+      </c>
+      <c r="G56" s="6">
+        <v>16</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+      <c r="D57" s="10">
+        <v>1</v>
+      </c>
+      <c r="E57" s="10">
+        <v>250</v>
+      </c>
+      <c r="F57" s="11">
+        <v>1801</v>
+      </c>
+      <c r="G57" s="6">
+        <v>16</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -24910,7 +24949,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -24922,7 +24961,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -24934,7 +24973,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -24946,7 +24985,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -24958,7 +24997,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -24970,7 +25009,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -24982,7 +25021,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -24994,7 +25033,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -25006,7 +25045,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -25018,7 +25057,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -25030,7 +25069,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -25042,7 +25081,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -25054,7 +25093,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -25066,7 +25105,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -25078,7 +25117,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -25090,7 +25129,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -25102,7 +25141,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -25114,7 +25153,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -25126,7 +25165,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -25138,7 +25177,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -25150,7 +25189,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -25162,7 +25201,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -25174,7 +25213,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -25186,7 +25225,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -25198,7 +25237,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -25210,7 +25249,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -25222,7 +25261,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -25234,7 +25273,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -25246,7 +25285,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -25258,7 +25297,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -25270,7 +25309,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -25282,7 +25321,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -25294,7 +25333,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -25306,7 +25345,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -25318,7 +25357,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -25330,7 +25369,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -25342,7 +25381,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -25354,7 +25393,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -25366,7 +25405,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -25378,7 +25417,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -25390,7 +25429,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -25402,7 +25441,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -25414,7 +25453,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -25426,7 +25465,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -25438,7 +25477,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -25450,7 +25489,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -25462,7 +25501,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -25474,7 +25513,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -25486,7 +25525,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -25498,7 +25537,7 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -25510,7 +25549,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -25522,7 +25561,7 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -25534,7 +25573,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -25546,7 +25585,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -25558,7 +25597,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -25570,7 +25609,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -25582,7 +25621,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -25594,7 +25633,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -25606,7 +25645,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>

--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DB\Projects\SW002-LoadWizardPro_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D403CEE-FF37-4285-8097-E4069CEE7935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B5DD33-760A-499A-B4BD-74690D56B084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10068" yWindow="792" windowWidth="17280" windowHeight="8880" tabRatio="607" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="607" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Robot FieldBus" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="287">
   <si>
     <t>Сигналы от Робота к ПЛК</t>
   </si>
@@ -658,12 +658,6 @@
     <t>Разворот вала перед возвратом в кондуктор</t>
   </si>
   <si>
-    <t>Параллельнй захват, длина L</t>
-  </si>
-  <si>
-    <t>Параллельнй захват, длина l</t>
-  </si>
-  <si>
     <t>Нижний лимит</t>
   </si>
   <si>
@@ -887,6 +881,24 @@
   </si>
   <si>
     <t>Сначала зажимается патрон, потом открывается захват</t>
+  </si>
+  <si>
+    <t>Параллельный захват до обработки, длина L</t>
+  </si>
+  <si>
+    <t>Параллельный захват до обработки, длина l</t>
+  </si>
+  <si>
+    <t>Параллельный захват, после обработки, длина L</t>
+  </si>
+  <si>
+    <t>Параллельный захват, после обработки, длина l</t>
+  </si>
+  <si>
+    <t>Параллельный захват, до обработки, длина L</t>
+  </si>
+  <si>
+    <t>Параллельный захват, до обработки, длина l</t>
   </si>
 </sst>
 </file>
@@ -1064,6 +1076,73 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1270,73 +1349,6 @@
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1351,52 +1363,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
   <autoFilter ref="A2:D898" xr:uid="{3542D272-09F4-499C-98E1-39E15F87CA4F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{01E43BCB-FF1F-49F0-8EDF-8BDB85A3A52E}" name="Адрес на роботе" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{E49880E5-7072-4525-BCB4-CE1A527AD7B0}" name="Программный адрес" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{01E43BCB-FF1F-49F0-8EDF-8BDB85A3A52E}" name="Адрес на роботе" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{E49880E5-7072-4525-BCB4-CE1A527AD7B0}" name="Программный адрес" dataDxfId="22">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(A3+65536-$A$3 +2*96, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6FB0113F-D5BD-4FC0-9B02-B55C66B93470}" name="Адрес слова" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{6FB0113F-D5BD-4FC0-9B02-B55C66B93470}" name="Адрес слова" dataDxfId="21">
       <calculatedColumnFormula>IF(RIGHT(B3,1)="0",LEFT(B3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4DE3B543-63F2-4F27-A542-D97E6805A269}" name="Комментарий" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{4DE3B543-63F2-4F27-A542-D97E6805A269}" name="Комментарий" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}" name="Таблица6" displayName="Таблица6" ref="F2:J898" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}" name="Таблица6" displayName="Таблица6" ref="F2:J898" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
   <autoFilter ref="F2:J898" xr:uid="{550A69A2-4B7A-432A-BE2D-B2C7757C7AFB}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B59749FC-B984-4636-91DE-503B7E13DCCC}" name="Адрес на роботе" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{26D947D3-C6E7-42A6-80AF-4F5F45D689B5}" name="Программный адрес" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{B59749FC-B984-4636-91DE-503B7E13DCCC}" name="Адрес на роботе" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{26D947D3-C6E7-42A6-80AF-4F5F45D689B5}" name="Программный адрес" dataDxfId="15">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(F3+65536+4096 +2* 96-$F$3, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2A6702CA-A964-4A02-89A8-180932C37848}" name="Адрес слова" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{2A6702CA-A964-4A02-89A8-180932C37848}" name="Адрес слова" dataDxfId="14">
       <calculatedColumnFormula>IF(RIGHT(G3,1)="0",LEFT(G3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{14C27F77-1D34-48C7-8407-3A45CEFDA494}" name="Комментарий" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{892E34D9-9BCE-4F6E-9C33-9F094BD6773A}" name="Столбец1" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{14C27F77-1D34-48C7-8407-3A45CEFDA494}" name="Комментарий" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{892E34D9-9BCE-4F6E-9C33-9F094BD6773A}" name="Столбец1" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}" name="Таблица35" displayName="Таблица35" ref="A1:H117" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}" name="Таблица35" displayName="Таблица35" ref="A1:H117" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
   <autoFilter ref="A1:H117" xr:uid="{B984F479-8F13-480A-9F94-8220CA7CC20B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{92D55AB5-DA85-4CE6-885A-51E3B1BAD618}" name="Физический адрес" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{74C09991-F50A-4EC3-9F41-CEBF1B9D9EBC}" name="Назначение" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{AE4EE521-2728-4FC7-BBC9-E3628F4E7893}" name="Комментарий" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{4340E727-5C89-4710-A72C-D3D49E41FCE8}" name="Нижний лимит" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{7E71D017-2529-42CC-875C-F0DFB0A1764E}" name="Верхний лимит" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{EEC6976F-E174-47AA-A6ED-83856650B659}" name="Адрес на роботе" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{3A79B632-BB55-4ACF-9B1F-ABA093E90E2C}" name="Кол-во бит на роботе" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{8C0B7855-A039-4C8A-91C5-142421D6FEF0}" name="Преобразование" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{92D55AB5-DA85-4CE6-885A-51E3B1BAD618}" name="Физический адрес" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{74C09991-F50A-4EC3-9F41-CEBF1B9D9EBC}" name="Назначение" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{AE4EE521-2728-4FC7-BBC9-E3628F4E7893}" name="Комментарий" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4340E727-5C89-4710-A72C-D3D49E41FCE8}" name="Нижний лимит" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{7E71D017-2529-42CC-875C-F0DFB0A1764E}" name="Верхний лимит" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{EEC6976F-E174-47AA-A6ED-83856650B659}" name="Адрес на роботе" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{3A79B632-BB55-4ACF-9B1F-ABA093E90E2C}" name="Кол-во бит на роботе" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{8C0B7855-A039-4C8A-91C5-142421D6FEF0}" name="Преобразование" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2163,7 +2175,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F16" s="1">
         <v>1078</v>
@@ -3134,7 +3146,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -4311,7 +4323,7 @@
         <v>P1006</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F99" s="1">
         <v>1161</v>
@@ -4701,7 +4713,7 @@
         <v>P1007</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F115" s="1">
         <v>1177</v>
@@ -4715,7 +4727,7 @@
         <v>P1107</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
@@ -5091,7 +5103,7 @@
         <v>P1008</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F131" s="1">
         <v>1193</v>
@@ -5105,7 +5117,7 @@
         <v>P1108</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
@@ -5481,7 +5493,7 @@
         <v>P1009</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F147" s="1">
         <v>1209</v>
@@ -5495,7 +5507,7 @@
         <v>P1109</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
@@ -5871,7 +5883,7 @@
         <v>P1010</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F163" s="1">
         <v>1225</v>
@@ -5885,7 +5897,7 @@
         <v>P1110</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -6080,7 +6092,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
@@ -6278,7 +6290,7 @@
         <v>P1111</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -6473,7 +6485,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -6671,7 +6683,7 @@
         <v>P1112</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
@@ -6866,7 +6878,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -7064,7 +7076,7 @@
         <v>P1113</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
@@ -7259,7 +7271,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
@@ -7443,7 +7455,7 @@
         <v>P1014</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F227" s="1">
         <v>1289</v>
@@ -7473,7 +7485,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F228" s="1">
         <v>1290</v>
@@ -7503,7 +7515,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F229" s="1">
         <v>1291</v>
@@ -7533,7 +7545,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F230" s="1">
         <v>1292</v>
@@ -7563,7 +7575,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F231" s="1">
         <v>1293</v>
@@ -7591,7 +7603,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F232" s="1">
         <v>1294</v>
@@ -7619,7 +7631,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F233" s="1">
         <v>1295</v>
@@ -7647,7 +7659,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F234" s="1">
         <v>1296</v>
@@ -7661,7 +7673,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I234" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
@@ -7677,7 +7689,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F235" s="1">
         <v>1297</v>
@@ -7691,7 +7703,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I235" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
@@ -7707,7 +7719,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F236" s="1">
         <v>1298</v>
@@ -7721,7 +7733,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I236" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
@@ -7737,7 +7749,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F237" s="1">
         <v>1299</v>
@@ -7765,7 +7777,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F238" s="1">
         <v>1300</v>
@@ -7793,7 +7805,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F239" s="1">
         <v>1301</v>
@@ -7821,7 +7833,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F240" s="1">
         <v>1302</v>
@@ -7849,7 +7861,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F241" s="1">
         <v>1303</v>
@@ -7877,7 +7889,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F242" s="1">
         <v>1304</v>
@@ -7904,7 +7916,7 @@
         <v>P1015</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F243" s="1">
         <v>1305</v>
@@ -7918,7 +7930,7 @@
         <v>P1115</v>
       </c>
       <c r="I243" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
@@ -7934,7 +7946,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F244" s="1">
         <v>1306</v>
@@ -7962,7 +7974,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F245" s="1">
         <v>1307</v>
@@ -8312,7 +8324,7 @@
         <v>P1116</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -8699,7 +8711,7 @@
         <v>P1117</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
@@ -9086,7 +9098,7 @@
         <v>P1118</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
@@ -9473,7 +9485,7 @@
         <v>P1119</v>
       </c>
       <c r="I307" s="6" t="s">
-        <v>206</v>
+        <v>285</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
@@ -9860,7 +9872,7 @@
         <v>P1120</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>207</v>
+        <v>286</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
@@ -10247,7 +10259,7 @@
         <v>P1121</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.3">
@@ -10634,7 +10646,7 @@
         <v>P1122</v>
       </c>
       <c r="I355" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
@@ -11120,7 +11132,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I375" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
@@ -11219,7 +11231,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I379" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
@@ -12575,7 +12587,7 @@
         <v>P1127</v>
       </c>
       <c r="I435" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
@@ -12674,7 +12686,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="I439" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.3">
@@ -12965,7 +12977,7 @@
         <v>P1128</v>
       </c>
       <c r="I451" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
@@ -13352,7 +13364,7 @@
         <v>P1129</v>
       </c>
       <c r="I467" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.3">
@@ -13739,7 +13751,7 @@
         <v>P1130</v>
       </c>
       <c r="I483" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.3">
@@ -14126,7 +14138,7 @@
         <v>P1131</v>
       </c>
       <c r="I499" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.3">
@@ -14513,7 +14525,7 @@
         <v>P1132</v>
       </c>
       <c r="I515" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.3">
@@ -14900,7 +14912,7 @@
         <v>P1133</v>
       </c>
       <c r="I531" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.3">
@@ -15287,7 +15299,7 @@
         <v>P1134</v>
       </c>
       <c r="I547" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.3">
@@ -15674,7 +15686,7 @@
         <v>P1135</v>
       </c>
       <c r="I563" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.3">
@@ -16062,7 +16074,7 @@
         <v>P1136</v>
       </c>
       <c r="I579" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.3">
@@ -16464,7 +16476,7 @@
         <v>P1137</v>
       </c>
       <c r="I595" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.3">
@@ -16860,7 +16872,7 @@
         <v>P1138</v>
       </c>
       <c r="I611" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.3">
@@ -17247,7 +17259,7 @@
         <v>P1139</v>
       </c>
       <c r="I627" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.3">
@@ -17634,7 +17646,7 @@
         <v>P1140</v>
       </c>
       <c r="I643" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.3">
@@ -18021,7 +18033,7 @@
         <v>P1141</v>
       </c>
       <c r="I659" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.3">
@@ -18408,7 +18420,7 @@
         <v>P1142</v>
       </c>
       <c r="I675" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.3">
@@ -18795,7 +18807,7 @@
         <v>P1143</v>
       </c>
       <c r="I691" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.3">
@@ -19183,7 +19195,7 @@
         <v>P1144</v>
       </c>
       <c r="I707" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="708" spans="1:9" x14ac:dyDescent="0.3">
@@ -19571,7 +19583,7 @@
         <v>P1145</v>
       </c>
       <c r="I723" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.3">
@@ -19958,7 +19970,7 @@
         <v>P1146</v>
       </c>
       <c r="I739" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.3">
@@ -20344,7 +20356,9 @@
         <f t="shared" si="51"/>
         <v>P1147</v>
       </c>
-      <c r="I755" s="3"/>
+      <c r="I755" s="6" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="756" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
@@ -20729,7 +20743,9 @@
         <f t="shared" si="51"/>
         <v>P1148</v>
       </c>
-      <c r="I771" s="3"/>
+      <c r="I771" s="6" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="772" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
@@ -23824,19 +23840,19 @@
         <v>5</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -23958,7 +23974,7 @@
         <v>193</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -23974,7 +23990,7 @@
         <v>194</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -23990,7 +24006,7 @@
         <v>195</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -24066,7 +24082,7 @@
         <v>85</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="10">
@@ -24082,7 +24098,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -24090,7 +24106,7 @@
         <v>86</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="10">
@@ -24106,7 +24122,7 @@
         <v>16</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -24114,7 +24130,7 @@
         <v>87</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="10">
@@ -24130,7 +24146,7 @@
         <v>16</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -24138,7 +24154,7 @@
         <v>88</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="10">
@@ -24154,7 +24170,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -24162,7 +24178,7 @@
         <v>89</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>206</v>
+        <v>281</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="10">
@@ -24178,7 +24194,7 @@
         <v>16</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -24186,7 +24202,7 @@
         <v>90</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>207</v>
+        <v>282</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="10">
@@ -24202,7 +24218,7 @@
         <v>16</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -24210,7 +24226,7 @@
         <v>91</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="10">
@@ -24226,7 +24242,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -24234,7 +24250,7 @@
         <v>92</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="10">
@@ -24250,7 +24266,7 @@
         <v>16</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -24292,7 +24308,7 @@
         <v>95</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6">
@@ -24314,7 +24330,7 @@
         <v>96</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6">
@@ -24414,7 +24430,7 @@
         <v>101</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6">
@@ -24436,7 +24452,7 @@
         <v>102</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6">
@@ -24458,7 +24474,7 @@
         <v>103</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="6">
@@ -24492,7 +24508,7 @@
         <v>105</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="10">
@@ -24508,7 +24524,7 @@
         <v>16</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -24516,7 +24532,7 @@
         <v>106</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="10">
@@ -24538,7 +24554,7 @@
         <v>107</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="10">
@@ -24554,7 +24570,7 @@
         <v>16</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -24562,7 +24578,7 @@
         <v>108</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="10">
@@ -24596,7 +24612,7 @@
         <v>110</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="10">
@@ -24612,7 +24628,7 @@
         <v>16</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -24620,7 +24636,7 @@
         <v>111</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="10">
@@ -24636,7 +24652,7 @@
         <v>16</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
@@ -24644,7 +24660,7 @@
         <v>112</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="10">
@@ -24660,7 +24676,7 @@
         <v>16</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -24668,7 +24684,7 @@
         <v>113</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="10">
@@ -24684,7 +24700,7 @@
         <v>16</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
@@ -24692,7 +24708,7 @@
         <v>114</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="10">
@@ -24708,7 +24724,7 @@
         <v>16</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -24716,7 +24732,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="10">
@@ -24732,7 +24748,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
@@ -24740,7 +24756,7 @@
         <v>116</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="10">
@@ -24756,7 +24772,7 @@
         <v>16</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -24764,7 +24780,7 @@
         <v>117</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="10">
@@ -24780,7 +24796,7 @@
         <v>16</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
@@ -24788,7 +24804,7 @@
         <v>118</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="10">
@@ -24804,7 +24820,7 @@
         <v>16</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -24812,7 +24828,7 @@
         <v>119</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="10">
@@ -24828,7 +24844,7 @@
         <v>16</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
@@ -24848,7 +24864,7 @@
         <v>121</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="6">
@@ -24870,7 +24886,7 @@
         <v>122</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C55" s="6"/>
       <c r="D55" s="6">
@@ -24892,7 +24908,7 @@
         <v>123</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="10">
@@ -24908,7 +24924,7 @@
         <v>16</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
@@ -24916,7 +24932,7 @@
         <v>124</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="10">
@@ -24932,7 +24948,7 @@
         <v>16</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -24951,25 +24967,49 @@
       <c r="A59" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B59" s="6"/>
+      <c r="B59" s="6" t="s">
+        <v>281</v>
+      </c>
       <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
+      <c r="D59" s="10">
+        <v>1</v>
+      </c>
+      <c r="E59" s="10">
+        <v>250</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1369</v>
+      </c>
+      <c r="G59" s="6">
+        <v>16</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B60" s="6"/>
+      <c r="B60" s="6" t="s">
+        <v>282</v>
+      </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
+      <c r="D60" s="10">
+        <v>1</v>
+      </c>
+      <c r="E60" s="10">
+        <v>250</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1385</v>
+      </c>
+      <c r="G60" s="6">
+        <v>16</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">

--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DB\Projects\SW002-LoadWizardPro_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B5DD33-760A-499A-B4BD-74690D56B084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C263C0F5-CD3A-4E2B-823F-3877EA647ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="607" xr2:uid="{6E79B54C-AC0C-4496-B3E1-735F763850AB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="293">
   <si>
     <t>Сигналы от Робота к ПЛК</t>
   </si>
@@ -899,6 +899,24 @@
   </si>
   <si>
     <t>Параллельный захват, до обработки, длина l</t>
+  </si>
+  <si>
+    <t>Параллельный захват после обработки, длина L</t>
+  </si>
+  <si>
+    <t>Параллельный захват после  обработки, длина l</t>
+  </si>
+  <si>
+    <t>Установ вала вглубь</t>
+  </si>
+  <si>
+    <t>Глубина при установке</t>
+  </si>
+  <si>
+    <t>Глубина при захвате</t>
+  </si>
+  <si>
+    <t>Захват огрызка</t>
   </si>
 </sst>
 </file>
@@ -7588,7 +7606,9 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I231" s="6"/>
+      <c r="I231" s="6" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
@@ -7616,7 +7636,9 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I232" s="6"/>
+      <c r="I232" s="6" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
@@ -21130,7 +21152,9 @@
         <f t="shared" si="55"/>
         <v>P1149</v>
       </c>
-      <c r="I787" s="3"/>
+      <c r="I787" s="6" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
@@ -21515,7 +21539,9 @@
         <f t="shared" si="55"/>
         <v>P1150</v>
       </c>
-      <c r="I803" s="3"/>
+      <c r="I803" s="6" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="804" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A804" s="1">
@@ -23937,7 +23963,9 @@
       <c r="A7" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -23949,7 +23977,9 @@
       <c r="A8" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>292</v>
+      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -24968,7 +24998,7 @@
         <v>126</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="10">
@@ -24992,7 +25022,7 @@
         <v>127</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="10">
@@ -25027,7 +25057,9 @@
       <c r="A62" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="6"/>
+      <c r="B62" s="6" t="s">
+        <v>290</v>
+      </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -25039,7 +25071,9 @@
       <c r="A63" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="6"/>
+      <c r="B63" s="6" t="s">
+        <v>291</v>
+      </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
